--- a/crates/unluminous-sheet/tests/fixtures/pages/pages-consolas.xlsx
+++ b/crates/unluminous-sheet/tests/fixtures/pages/pages-consolas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jason\dev\unluminous\.claude\worktrees\agent-afa636fef9f2b0676\crates\unluminous-sheet\tests\fixtures\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{159C0E8E-F032-4422-9ABC-C7BB57572F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F5405F8-9CA0-4AB1-A6A5-035FA1377307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="6660" windowWidth="43200" windowHeight="23445" activeTab="6" xr2:uid="{D4D811FB-116A-44AB-A74F-DB47ED86A3ED}"/>
+    <workbookView xWindow="1875" yWindow="6660" windowWidth="43200" windowHeight="23445" activeTab="6" xr2:uid="{6E1ACE24-E534-4304-86F8-910CC3C7F0B6}"/>
   </bookViews>
   <sheets>
     <sheet name="letter-p" sheetId="1" r:id="rId1"/>
@@ -412,7 +412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB6FF4A-9232-4F37-9CEC-FE73650983FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFCF8E30-1D3E-4A88-B491-7D460E2A3A37}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -16283,7 +16283,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B791E095-4CBF-4AB2-8FE7-530186CED95B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59017A4D-D5C3-4805-8796-E8E4714482E6}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -32154,7 +32154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F80A59-A9EF-448F-B20F-0BBA2BC54E7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3796384-7DDD-41FF-87BC-B5D5BC60BDC9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -48028,7 +48028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AF4EDF-1C81-482F-9ACF-085F92BDA0D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F734DBE1-8B80-4861-A9D7-ADE70FCB4045}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -63902,7 +63902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85307456-89F1-4F5A-A0FD-FF3504318F6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E3DF736-3D0C-4FAF-84DC-2755B430B773}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -79773,7 +79773,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CD41EA-2210-4667-B0BE-4969888BCAE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A54E7B-6AFD-4B16-993C-D1685990750B}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -95644,7 +95644,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446BCF1F-636D-4B71-8B28-D3331A8ECB9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33AAE2AE-E239-461F-AB40-9289A0466219}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
